--- a/gant graph.xlsx
+++ b/gant graph.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LYL114\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\fcous\AE WPM Demo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B104276E-ACDC-44B1-93BB-F6D0D3883699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F53008-86FA-4931-AB57-F31E00F965EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{852EBC35-2D13-4E07-8F25-882988BABC80}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{852EBC35-2D13-4E07-8F25-882988BABC80}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Gantt" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Project Gantt'!$A$3:$H$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Project Gantt'!$A$3:$H$34</definedName>
     <definedName name="Actual" localSheetId="0">('Project Gantt'!PeriodInActual*(#REF!&gt;0))*'Project Gantt'!PeriodInPlan</definedName>
     <definedName name="Actual">(PeriodInActual*(#REF!&gt;0))*PeriodInPlan</definedName>
     <definedName name="ActualBeyond" localSheetId="0">'Project Gantt'!PeriodInActual*(#REF!&gt;0)</definedName>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="125">
   <si>
     <t>Project Phase</t>
   </si>
@@ -246,220 +246,233 @@
     <t>Project</t>
   </si>
   <si>
+    <t>Hypercare Exit Success Criteria Review</t>
+  </si>
+  <si>
+    <t>FBP approval</t>
+  </si>
+  <si>
+    <t>Functional head approval</t>
+  </si>
+  <si>
+    <t>ELT approg</t>
+  </si>
+  <si>
+    <t>GSC Head -1 approval</t>
+  </si>
+  <si>
+    <t>Opportunity Assessment (Detailed task scoping)</t>
+  </si>
+  <si>
+    <t>PID Approval</t>
+  </si>
+  <si>
+    <t>Hiring Request approval</t>
+  </si>
+  <si>
+    <t>Resource mobilization</t>
+  </si>
+  <si>
+    <t>NEO + GSC L&amp;D business &amp; training stage</t>
+  </si>
+  <si>
+    <t>Knowledge Transfer Business + System Training sessions + Assessments</t>
+  </si>
+  <si>
+    <t>Volume Transfer/Ramp-up stage</t>
+  </si>
+  <si>
+    <t>Hypercare stage</t>
+  </si>
+  <si>
+    <t>Recommended soonest Capacity Release</t>
+  </si>
+  <si>
+    <t>Migration Sign-off recommendation</t>
+  </si>
+  <si>
+    <t>Calendar weeks</t>
+  </si>
+  <si>
+    <t>Timeline weeks</t>
+  </si>
+  <si>
+    <t>wk01</t>
+  </si>
+  <si>
+    <t>wk02</t>
+  </si>
+  <si>
+    <t>wk03</t>
+  </si>
+  <si>
+    <t>wk04</t>
+  </si>
+  <si>
+    <t>wk05</t>
+  </si>
+  <si>
+    <t>wk06</t>
+  </si>
+  <si>
+    <t>wk07</t>
+  </si>
+  <si>
+    <t>wk08</t>
+  </si>
+  <si>
+    <t>wk09</t>
+  </si>
+  <si>
+    <t>wk10</t>
+  </si>
+  <si>
+    <t>wk11</t>
+  </si>
+  <si>
+    <t>wk12</t>
+  </si>
+  <si>
+    <t>wk13</t>
+  </si>
+  <si>
+    <t>wk14</t>
+  </si>
+  <si>
+    <t>wk15</t>
+  </si>
+  <si>
+    <t>wk16</t>
+  </si>
+  <si>
+    <t>wk17</t>
+  </si>
+  <si>
+    <t>wk18</t>
+  </si>
+  <si>
+    <t>wk19</t>
+  </si>
+  <si>
+    <t>wk20</t>
+  </si>
+  <si>
+    <t>wk21</t>
+  </si>
+  <si>
+    <t>wk22</t>
+  </si>
+  <si>
+    <t>wk23</t>
+  </si>
+  <si>
+    <t>wk24</t>
+  </si>
+  <si>
+    <t>wk25</t>
+  </si>
+  <si>
+    <t>wk26</t>
+  </si>
+  <si>
+    <t>wk27</t>
+  </si>
+  <si>
+    <t>wk28</t>
+  </si>
+  <si>
+    <t>wk29</t>
+  </si>
+  <si>
+    <t>wk30</t>
+  </si>
+  <si>
+    <t>wk31</t>
+  </si>
+  <si>
+    <t>wk32</t>
+  </si>
+  <si>
+    <t>wk33</t>
+  </si>
+  <si>
+    <t>wk34</t>
+  </si>
+  <si>
+    <t>wk35</t>
+  </si>
+  <si>
+    <t>wk36</t>
+  </si>
+  <si>
+    <t>wk37</t>
+  </si>
+  <si>
+    <t>wk38</t>
+  </si>
+  <si>
+    <t>wk39</t>
+  </si>
+  <si>
+    <t>wk40</t>
+  </si>
+  <si>
+    <t>wk41</t>
+  </si>
+  <si>
+    <t>wk42</t>
+  </si>
+  <si>
+    <t>Wk11</t>
+  </si>
+  <si>
+    <t>Wk12</t>
+  </si>
+  <si>
+    <t>Wk13</t>
+  </si>
+  <si>
+    <t>PID approval</t>
+  </si>
+  <si>
+    <t>request window is first 15 days of the monht</t>
+  </si>
+  <si>
+    <t>reply period of that request: by end of the respective monht</t>
+  </si>
+  <si>
+    <t>create the hiring approval request: approved every two weeks of each month</t>
+  </si>
+  <si>
+    <t>workday requisition - that takes about a week</t>
+  </si>
+  <si>
+    <t>Wk9</t>
+  </si>
+  <si>
+    <t>Wk10</t>
+  </si>
+  <si>
+    <t>wk43</t>
+  </si>
+  <si>
+    <t>wk44</t>
+  </si>
+  <si>
     <t>Business Case (Memo)</t>
-  </si>
-  <si>
-    <t>Hypercare Exit Success Criteria Review</t>
-  </si>
-  <si>
-    <t>FBP approval</t>
-  </si>
-  <si>
-    <t>Functional head approval</t>
-  </si>
-  <si>
-    <t>ELT approg</t>
-  </si>
-  <si>
-    <t>GSC Head -1 approval</t>
-  </si>
-  <si>
-    <t>Opportunity Assessment (Detailed task scoping)</t>
-  </si>
-  <si>
-    <t>PID Approval</t>
-  </si>
-  <si>
-    <t>Hiring Request approval</t>
-  </si>
-  <si>
-    <t>Resource mobilization</t>
-  </si>
-  <si>
-    <t>NEO + GSC L&amp;D business &amp; training stage</t>
-  </si>
-  <si>
-    <t>Knowledge Transfer Business + System Training sessions + Assessments</t>
-  </si>
-  <si>
-    <t>Volume Transfer/Ramp-up stage</t>
-  </si>
-  <si>
-    <t>Hypercare stage</t>
-  </si>
-  <si>
-    <t>Recommended soonest Capacity Release</t>
-  </si>
-  <si>
-    <t>Migration Sign-off recommendation</t>
-  </si>
-  <si>
-    <t>Calendar weeks</t>
-  </si>
-  <si>
-    <t>Timeline weeks</t>
-  </si>
-  <si>
-    <t>wk01</t>
-  </si>
-  <si>
-    <t>wk02</t>
-  </si>
-  <si>
-    <t>wk03</t>
-  </si>
-  <si>
-    <t>wk04</t>
-  </si>
-  <si>
-    <t>wk05</t>
-  </si>
-  <si>
-    <t>wk06</t>
-  </si>
-  <si>
-    <t>wk07</t>
-  </si>
-  <si>
-    <t>wk08</t>
-  </si>
-  <si>
-    <t>wk09</t>
-  </si>
-  <si>
-    <t>wk10</t>
-  </si>
-  <si>
-    <t>wk11</t>
-  </si>
-  <si>
-    <t>wk12</t>
-  </si>
-  <si>
-    <t>wk13</t>
-  </si>
-  <si>
-    <t>wk14</t>
-  </si>
-  <si>
-    <t>wk15</t>
-  </si>
-  <si>
-    <t>wk16</t>
-  </si>
-  <si>
-    <t>wk17</t>
-  </si>
-  <si>
-    <t>wk18</t>
-  </si>
-  <si>
-    <t>wk19</t>
-  </si>
-  <si>
-    <t>wk20</t>
-  </si>
-  <si>
-    <t>wk21</t>
-  </si>
-  <si>
-    <t>wk22</t>
-  </si>
-  <si>
-    <t>wk23</t>
-  </si>
-  <si>
-    <t>wk24</t>
-  </si>
-  <si>
-    <t>wk25</t>
-  </si>
-  <si>
-    <t>wk26</t>
-  </si>
-  <si>
-    <t>wk27</t>
-  </si>
-  <si>
-    <t>wk28</t>
-  </si>
-  <si>
-    <t>wk29</t>
-  </si>
-  <si>
-    <t>wk30</t>
-  </si>
-  <si>
-    <t>wk31</t>
-  </si>
-  <si>
-    <t>wk32</t>
-  </si>
-  <si>
-    <t>wk33</t>
-  </si>
-  <si>
-    <t>wk34</t>
-  </si>
-  <si>
-    <t>wk35</t>
-  </si>
-  <si>
-    <t>wk36</t>
-  </si>
-  <si>
-    <t>wk37</t>
-  </si>
-  <si>
-    <t>wk38</t>
-  </si>
-  <si>
-    <t>wk39</t>
-  </si>
-  <si>
-    <t>wk40</t>
-  </si>
-  <si>
-    <t>wk41</t>
-  </si>
-  <si>
-    <t>wk42</t>
-  </si>
-  <si>
-    <t>Wk11</t>
-  </si>
-  <si>
-    <t>Wk12</t>
-  </si>
-  <si>
-    <t>Wk13</t>
-  </si>
-  <si>
-    <t>PID approval</t>
-  </si>
-  <si>
-    <t>request window is first 15 days of the monht</t>
-  </si>
-  <si>
-    <t>reply period of that request: by end of the respective monht</t>
-  </si>
-  <si>
-    <t>create the hiring approval request: approved every two weeks of each month</t>
-  </si>
-  <si>
-    <t>workday requisition - that takes about a week</t>
-  </si>
-  <si>
-    <t>Wk9</t>
-  </si>
-  <si>
-    <t>Wk10</t>
-  </si>
-  <si>
-    <t>wk43</t>
-  </si>
-  <si>
-    <t>wk44</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>STANDARD</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLAN(edit)</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>Actual(green,red)</t>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -563,7 +576,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -606,8 +619,20 @@
         <bgColor auto="1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="lightDown">
+        <fgColor auto="1"/>
+        <bgColor rgb="FF00B0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="lightDown">
+        <fgColor auto="1"/>
+        <bgColor rgb="FF00B050"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -680,12 +705,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -789,6 +845,21 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -911,7 +982,7 @@
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>264031</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>51954</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -3655,7 +3726,7 @@
   <sheetPr>
     <tabColor theme="1"/>
   </sheetPr>
-  <dimension ref="A1:BB29"/>
+  <dimension ref="A1:BB32"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" outlineLevelRow="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="8.5" customWidth="1"/>
@@ -3721,22 +3792,22 @@
         <v>8</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K3" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="L3" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="L3" s="4" t="s">
-        <v>119</v>
-      </c>
       <c r="M3" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="N3" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="O3" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>112</v>
       </c>
       <c r="P3" s="4" t="s">
         <v>9</v>
@@ -3867,139 +3938,139 @@
       <c r="H4" s="30"/>
       <c r="I4" s="32"/>
       <c r="J4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K4" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="L4" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="M4" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="N4" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="O4" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="P4" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="Q4" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="Q4" s="4" t="s">
+      <c r="R4" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="R4" s="4" t="s">
+      <c r="S4" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="S4" s="4" t="s">
+      <c r="T4" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="T4" s="4" t="s">
+      <c r="U4" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="U4" s="4" t="s">
+      <c r="V4" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="V4" s="4" t="s">
+      <c r="W4" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="W4" s="4" t="s">
+      <c r="X4" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="X4" s="4" t="s">
+      <c r="Y4" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="Y4" s="4" t="s">
+      <c r="Z4" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="Z4" s="4" t="s">
+      <c r="AA4" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="AA4" s="4" t="s">
+      <c r="AB4" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="AB4" s="4" t="s">
+      <c r="AC4" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="AC4" s="4" t="s">
+      <c r="AD4" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="AD4" s="4" t="s">
+      <c r="AE4" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="AE4" s="4" t="s">
+      <c r="AF4" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="AF4" s="4" t="s">
+      <c r="AG4" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="AG4" s="4" t="s">
+      <c r="AH4" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="AH4" s="4" t="s">
+      <c r="AI4" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="AI4" s="4" t="s">
+      <c r="AJ4" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="AJ4" s="4" t="s">
+      <c r="AK4" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="AK4" s="4" t="s">
+      <c r="AL4" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="AL4" s="4" t="s">
+      <c r="AM4" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="AM4" s="4" t="s">
+      <c r="AN4" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="AN4" s="4" t="s">
+      <c r="AO4" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="AO4" s="4" t="s">
+      <c r="AP4" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="AP4" s="4" t="s">
+      <c r="AQ4" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="AQ4" s="4" t="s">
+      <c r="AR4" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="AR4" s="4" t="s">
+      <c r="AS4" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="AS4" s="4" t="s">
+      <c r="AT4" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="AT4" s="4" t="s">
+      <c r="AU4" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="AU4" s="4" t="s">
+      <c r="AV4" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="AV4" s="4" t="s">
+      <c r="AW4" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="AW4" s="4" t="s">
+      <c r="AX4" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="AX4" s="4" t="s">
+      <c r="AY4" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="AY4" s="4" t="s">
+      <c r="AZ4" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="AZ4" s="4" t="s">
-        <v>109</v>
-      </c>
       <c r="BA4" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="BB4" s="4" t="s">
         <v>120</v>
-      </c>
-      <c r="BB4" s="4" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:54" s="2" customFormat="1" ht="15" customHeight="1">
@@ -4153,10 +4224,12 @@
     </row>
     <row r="7" spans="1:54" outlineLevel="1">
       <c r="G7" s="17"/>
-      <c r="I7" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="J7" s="18"/>
+      <c r="I7" s="36" t="s">
+        <v>121</v>
+      </c>
+      <c r="J7" s="18" t="s">
+        <v>122</v>
+      </c>
       <c r="K7" s="20"/>
       <c r="L7" s="20"/>
       <c r="M7" s="20"/>
@@ -4204,15 +4277,15 @@
     </row>
     <row r="8" spans="1:54" outlineLevel="1">
       <c r="G8" s="17"/>
-      <c r="I8" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="J8" s="18"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="20"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="K8" s="39"/>
+      <c r="L8" s="39"/>
+      <c r="M8" s="39"/>
+      <c r="N8" s="39"/>
+      <c r="O8" s="19"/>
       <c r="P8" s="19"/>
       <c r="Q8" s="19"/>
       <c r="R8" s="19"/>
@@ -4254,17 +4327,17 @@
       <c r="BB8" s="19"/>
     </row>
     <row r="9" spans="1:54" outlineLevel="1">
-      <c r="H9" s="21"/>
-      <c r="I9" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" s="22"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="20"/>
+      <c r="G9" s="17"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="K9" s="40"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
       <c r="Q9" s="19"/>
       <c r="R9" s="19"/>
       <c r="S9" s="19"/>
@@ -4305,9 +4378,9 @@
       <c r="BB9" s="19"/>
     </row>
     <row r="10" spans="1:54" outlineLevel="1">
-      <c r="H10" s="21"/>
+      <c r="G10" s="17"/>
       <c r="I10" s="18" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="J10" s="18"/>
       <c r="K10" s="19"/>
@@ -4315,7 +4388,7 @@
       <c r="M10" s="19"/>
       <c r="N10" s="19"/>
       <c r="O10" s="20"/>
-      <c r="P10" s="20"/>
+      <c r="P10" s="19"/>
       <c r="Q10" s="19"/>
       <c r="R10" s="19"/>
       <c r="S10" s="19"/>
@@ -4356,17 +4429,15 @@
       <c r="BB10" s="19"/>
     </row>
     <row r="11" spans="1:54" outlineLevel="1">
-      <c r="H11" s="21"/>
-      <c r="I11" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="J11" s="22"/>
+      <c r="G11" s="17"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
       <c r="K11" s="19"/>
       <c r="L11" s="19"/>
       <c r="M11" s="19"/>
       <c r="N11" s="19"/>
       <c r="O11" s="20"/>
-      <c r="P11" s="20"/>
+      <c r="P11" s="19"/>
       <c r="Q11" s="19"/>
       <c r="R11" s="19"/>
       <c r="S11" s="19"/>
@@ -4407,16 +4478,17 @@
       <c r="BB11" s="19"/>
     </row>
     <row r="12" spans="1:54" outlineLevel="1">
+      <c r="H12" s="21"/>
       <c r="I12" s="22" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="J12" s="22"/>
-      <c r="K12" s="20"/>
-      <c r="L12" s="20"/>
-      <c r="M12" s="20"/>
-      <c r="N12" s="20"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
       <c r="Q12" s="19"/>
       <c r="R12" s="19"/>
       <c r="S12" s="19"/>
@@ -4457,22 +4529,23 @@
       <c r="BB12" s="19"/>
     </row>
     <row r="13" spans="1:54" outlineLevel="1">
-      <c r="I13" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="J13" s="22"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="J13" s="18"/>
       <c r="K13" s="19"/>
       <c r="L13" s="19"/>
       <c r="M13" s="19"/>
       <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
-      <c r="P13" s="19"/>
-      <c r="Q13" s="20"/>
-      <c r="R13" s="20"/>
-      <c r="S13" s="20"/>
-      <c r="T13" s="20"/>
-      <c r="U13" s="20"/>
-      <c r="V13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
       <c r="W13" s="19"/>
       <c r="X13" s="19"/>
       <c r="Y13" s="19"/>
@@ -4506,31 +4579,24 @@
       <c r="BA13" s="19"/>
       <c r="BB13" s="19"/>
     </row>
-    <row r="14" spans="1:54" s="2" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
-      <c r="A14" s="23"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="J14" s="18"/>
+    <row r="14" spans="1:54" outlineLevel="1">
+      <c r="H14" s="21"/>
+      <c r="I14" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="J14" s="22"/>
       <c r="K14" s="19"/>
       <c r="L14" s="19"/>
       <c r="M14" s="19"/>
       <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="P14" s="19"/>
-      <c r="Q14" s="20"/>
-      <c r="R14" s="20"/>
-      <c r="S14" s="20"/>
-      <c r="T14" s="20"/>
-      <c r="U14" s="20"/>
-      <c r="V14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="19"/>
       <c r="W14" s="19"/>
       <c r="X14" s="19"/>
       <c r="Y14" s="19"/>
@@ -4564,23 +4630,15 @@
       <c r="BA14" s="19"/>
       <c r="BB14" s="19"/>
     </row>
-    <row r="15" spans="1:54" s="2" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
-      <c r="A15" s="23"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="25"/>
-      <c r="D15"/>
-      <c r="E15"/>
-      <c r="F15"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
+    <row r="15" spans="1:54" outlineLevel="1">
       <c r="I15" s="22" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="J15" s="22"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="19"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
       <c r="O15" s="19"/>
       <c r="P15" s="19"/>
       <c r="Q15" s="19"/>
@@ -4589,18 +4647,18 @@
       <c r="T15" s="19"/>
       <c r="U15" s="19"/>
       <c r="V15" s="19"/>
-      <c r="W15" s="20"/>
-      <c r="X15" s="20"/>
-      <c r="Y15" s="20"/>
-      <c r="Z15" s="20"/>
-      <c r="AA15" s="20"/>
-      <c r="AB15" s="20"/>
-      <c r="AC15" s="20"/>
-      <c r="AD15" s="20"/>
-      <c r="AE15" s="20"/>
-      <c r="AF15" s="20"/>
-      <c r="AG15" s="20"/>
-      <c r="AH15" s="20"/>
+      <c r="W15" s="19"/>
+      <c r="X15" s="19"/>
+      <c r="Y15" s="19"/>
+      <c r="Z15" s="19"/>
+      <c r="AA15" s="19"/>
+      <c r="AB15" s="19"/>
+      <c r="AC15" s="19"/>
+      <c r="AD15" s="19"/>
+      <c r="AE15" s="19"/>
+      <c r="AF15" s="19"/>
+      <c r="AG15" s="19"/>
+      <c r="AH15" s="19"/>
       <c r="AI15" s="19"/>
       <c r="AJ15" s="19"/>
       <c r="AK15" s="19"/>
@@ -4622,17 +4680,9 @@
       <c r="BA15" s="19"/>
       <c r="BB15" s="19"/>
     </row>
-    <row r="16" spans="1:54" s="2" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="25"/>
-      <c r="D16"/>
-      <c r="E16"/>
-      <c r="F16"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
+    <row r="16" spans="1:54" outlineLevel="1">
       <c r="I16" s="22" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J16" s="22"/>
       <c r="K16" s="19"/>
@@ -4641,12 +4691,12 @@
       <c r="N16" s="19"/>
       <c r="O16" s="19"/>
       <c r="P16" s="19"/>
-      <c r="Q16" s="19"/>
-      <c r="R16" s="19"/>
-      <c r="S16" s="19"/>
-      <c r="T16" s="19"/>
-      <c r="U16" s="19"/>
-      <c r="V16" s="19"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="20"/>
+      <c r="T16" s="20"/>
+      <c r="U16" s="20"/>
+      <c r="V16" s="20"/>
       <c r="W16" s="19"/>
       <c r="X16" s="19"/>
       <c r="Y16" s="19"/>
@@ -4659,8 +4709,8 @@
       <c r="AF16" s="19"/>
       <c r="AG16" s="19"/>
       <c r="AH16" s="19"/>
-      <c r="AI16" s="20"/>
-      <c r="AJ16" s="20"/>
+      <c r="AI16" s="19"/>
+      <c r="AJ16" s="19"/>
       <c r="AK16" s="19"/>
       <c r="AL16" s="19"/>
       <c r="AM16" s="19"/>
@@ -4684,27 +4734,27 @@
       <c r="A17" s="23"/>
       <c r="B17" s="24"/>
       <c r="C17" s="25"/>
-      <c r="D17"/>
-      <c r="E17"/>
-      <c r="F17"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
       <c r="G17" s="26"/>
       <c r="H17" s="26"/>
-      <c r="I17" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="J17" s="22"/>
+      <c r="I17" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="J17" s="18"/>
       <c r="K17" s="19"/>
       <c r="L17" s="19"/>
       <c r="M17" s="19"/>
       <c r="N17" s="19"/>
       <c r="O17" s="19"/>
       <c r="P17" s="19"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="19"/>
-      <c r="S17" s="19"/>
-      <c r="T17" s="19"/>
-      <c r="U17" s="19"/>
-      <c r="V17" s="19"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="20"/>
+      <c r="T17" s="20"/>
+      <c r="U17" s="20"/>
+      <c r="V17" s="20"/>
       <c r="W17" s="19"/>
       <c r="X17" s="19"/>
       <c r="Y17" s="19"/>
@@ -4719,10 +4769,10 @@
       <c r="AH17" s="19"/>
       <c r="AI17" s="19"/>
       <c r="AJ17" s="19"/>
-      <c r="AK17" s="20"/>
-      <c r="AL17" s="20"/>
-      <c r="AM17" s="20"/>
-      <c r="AN17" s="20"/>
+      <c r="AK17" s="19"/>
+      <c r="AL17" s="19"/>
+      <c r="AM17" s="19"/>
+      <c r="AN17" s="19"/>
       <c r="AO17" s="19"/>
       <c r="AP17" s="19"/>
       <c r="AQ17" s="19"/>
@@ -4748,7 +4798,7 @@
       <c r="G18" s="26"/>
       <c r="H18" s="26"/>
       <c r="I18" s="22" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="J18" s="22"/>
       <c r="K18" s="19"/>
@@ -4763,28 +4813,28 @@
       <c r="T18" s="19"/>
       <c r="U18" s="19"/>
       <c r="V18" s="19"/>
-      <c r="W18" s="19"/>
-      <c r="X18" s="19"/>
-      <c r="Y18" s="19"/>
-      <c r="Z18" s="19"/>
-      <c r="AA18" s="19"/>
-      <c r="AB18" s="19"/>
-      <c r="AC18" s="19"/>
-      <c r="AD18" s="19"/>
-      <c r="AE18" s="19"/>
-      <c r="AF18" s="19"/>
-      <c r="AG18" s="19"/>
-      <c r="AH18" s="19"/>
+      <c r="W18" s="20"/>
+      <c r="X18" s="20"/>
+      <c r="Y18" s="20"/>
+      <c r="Z18" s="20"/>
+      <c r="AA18" s="20"/>
+      <c r="AB18" s="20"/>
+      <c r="AC18" s="20"/>
+      <c r="AD18" s="20"/>
+      <c r="AE18" s="20"/>
+      <c r="AF18" s="20"/>
+      <c r="AG18" s="20"/>
+      <c r="AH18" s="20"/>
       <c r="AI18" s="19"/>
       <c r="AJ18" s="19"/>
       <c r="AK18" s="19"/>
       <c r="AL18" s="19"/>
       <c r="AM18" s="19"/>
       <c r="AN18" s="19"/>
-      <c r="AO18" s="20"/>
-      <c r="AP18" s="20"/>
-      <c r="AQ18" s="20"/>
-      <c r="AR18" s="20"/>
+      <c r="AO18" s="19"/>
+      <c r="AP18" s="19"/>
+      <c r="AQ18" s="19"/>
+      <c r="AR18" s="19"/>
       <c r="AS18" s="19"/>
       <c r="AT18" s="19"/>
       <c r="AU18" s="19"/>
@@ -4806,7 +4856,7 @@
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
       <c r="I19" s="22" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="J19" s="22"/>
       <c r="K19" s="19"/>
@@ -4833,8 +4883,8 @@
       <c r="AF19" s="19"/>
       <c r="AG19" s="19"/>
       <c r="AH19" s="19"/>
-      <c r="AI19" s="19"/>
-      <c r="AJ19" s="19"/>
+      <c r="AI19" s="20"/>
+      <c r="AJ19" s="20"/>
       <c r="AK19" s="19"/>
       <c r="AL19" s="19"/>
       <c r="AM19" s="19"/>
@@ -4843,10 +4893,10 @@
       <c r="AP19" s="19"/>
       <c r="AQ19" s="19"/>
       <c r="AR19" s="19"/>
-      <c r="AS19" s="20"/>
-      <c r="AT19" s="20"/>
-      <c r="AU19" s="20"/>
-      <c r="AV19" s="20"/>
+      <c r="AS19" s="19"/>
+      <c r="AT19" s="19"/>
+      <c r="AU19" s="19"/>
+      <c r="AV19" s="19"/>
       <c r="AW19" s="19"/>
       <c r="AX19" s="19"/>
       <c r="AY19" s="19"/>
@@ -4864,7 +4914,7 @@
       <c r="G20" s="26"/>
       <c r="H20" s="26"/>
       <c r="I20" s="22" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="J20" s="22"/>
       <c r="K20" s="19"/>
@@ -4893,10 +4943,10 @@
       <c r="AH20" s="19"/>
       <c r="AI20" s="19"/>
       <c r="AJ20" s="19"/>
-      <c r="AK20" s="19"/>
-      <c r="AL20" s="19"/>
-      <c r="AM20" s="19"/>
-      <c r="AN20" s="19"/>
+      <c r="AK20" s="20"/>
+      <c r="AL20" s="20"/>
+      <c r="AM20" s="20"/>
+      <c r="AN20" s="20"/>
       <c r="AO20" s="19"/>
       <c r="AP20" s="19"/>
       <c r="AQ20" s="19"/>
@@ -4905,7 +4955,7 @@
       <c r="AT20" s="19"/>
       <c r="AU20" s="19"/>
       <c r="AV20" s="19"/>
-      <c r="AW20" s="20"/>
+      <c r="AW20" s="19"/>
       <c r="AX20" s="19"/>
       <c r="AY20" s="19"/>
       <c r="AZ20" s="19"/>
@@ -4916,13 +4966,13 @@
       <c r="A21" s="23"/>
       <c r="B21" s="24"/>
       <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
+      <c r="D21"/>
+      <c r="E21"/>
+      <c r="F21"/>
+      <c r="G21" s="26"/>
       <c r="H21" s="26"/>
       <c r="I21" s="22" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="J21" s="22"/>
       <c r="K21" s="19"/>
@@ -4955,16 +5005,16 @@
       <c r="AL21" s="19"/>
       <c r="AM21" s="19"/>
       <c r="AN21" s="19"/>
-      <c r="AO21" s="19"/>
-      <c r="AP21" s="19"/>
-      <c r="AQ21" s="19"/>
-      <c r="AR21" s="19"/>
+      <c r="AO21" s="20"/>
+      <c r="AP21" s="20"/>
+      <c r="AQ21" s="20"/>
+      <c r="AR21" s="20"/>
       <c r="AS21" s="19"/>
       <c r="AT21" s="19"/>
       <c r="AU21" s="19"/>
       <c r="AV21" s="19"/>
       <c r="AW21" s="19"/>
-      <c r="AX21" s="20"/>
+      <c r="AX21" s="19"/>
       <c r="AY21" s="19"/>
       <c r="AZ21" s="19"/>
       <c r="BA21" s="19"/>
@@ -4974,13 +5024,13 @@
       <c r="A22" s="23"/>
       <c r="B22" s="24"/>
       <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="G22" s="26"/>
       <c r="H22" s="26"/>
       <c r="I22" s="22" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J22" s="22"/>
       <c r="K22" s="19"/>
@@ -5017,44 +5067,219 @@
       <c r="AP22" s="19"/>
       <c r="AQ22" s="19"/>
       <c r="AR22" s="19"/>
-      <c r="AS22" s="19"/>
-      <c r="AT22" s="19"/>
-      <c r="AU22" s="19"/>
-      <c r="AV22" s="19"/>
+      <c r="AS22" s="20"/>
+      <c r="AT22" s="20"/>
+      <c r="AU22" s="20"/>
+      <c r="AV22" s="20"/>
       <c r="AW22" s="19"/>
       <c r="AX22" s="19"/>
       <c r="AY22" s="19"/>
       <c r="AZ22" s="19"/>
-      <c r="BA22" s="20"/>
+      <c r="BA22" s="19"/>
       <c r="BB22" s="19"/>
     </row>
-    <row r="25" spans="1:54">
-      <c r="I25" s="29" t="s">
-        <v>113</v>
-      </c>
+    <row r="23" spans="1:54" s="2" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
+      <c r="A23" s="23"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="25"/>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="J23" s="22"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
+      <c r="R23" s="19"/>
+      <c r="S23" s="19"/>
+      <c r="T23" s="19"/>
+      <c r="U23" s="19"/>
+      <c r="V23" s="19"/>
+      <c r="W23" s="19"/>
+      <c r="X23" s="19"/>
+      <c r="Y23" s="19"/>
+      <c r="Z23" s="19"/>
+      <c r="AA23" s="19"/>
+      <c r="AB23" s="19"/>
+      <c r="AC23" s="19"/>
+      <c r="AD23" s="19"/>
+      <c r="AE23" s="19"/>
+      <c r="AF23" s="19"/>
+      <c r="AG23" s="19"/>
+      <c r="AH23" s="19"/>
+      <c r="AI23" s="19"/>
+      <c r="AJ23" s="19"/>
+      <c r="AK23" s="19"/>
+      <c r="AL23" s="19"/>
+      <c r="AM23" s="19"/>
+      <c r="AN23" s="19"/>
+      <c r="AO23" s="19"/>
+      <c r="AP23" s="19"/>
+      <c r="AQ23" s="19"/>
+      <c r="AR23" s="19"/>
+      <c r="AS23" s="19"/>
+      <c r="AT23" s="19"/>
+      <c r="AU23" s="19"/>
+      <c r="AV23" s="19"/>
+      <c r="AW23" s="20"/>
+      <c r="AX23" s="19"/>
+      <c r="AY23" s="19"/>
+      <c r="AZ23" s="19"/>
+      <c r="BA23" s="19"/>
+      <c r="BB23" s="19"/>
     </row>
-    <row r="26" spans="1:54">
-      <c r="I26" s="29" t="s">
-        <v>114</v>
-      </c>
+    <row r="24" spans="1:54" s="2" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
+      <c r="A24" s="23"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="J24" s="22"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
+      <c r="R24" s="19"/>
+      <c r="S24" s="19"/>
+      <c r="T24" s="19"/>
+      <c r="U24" s="19"/>
+      <c r="V24" s="19"/>
+      <c r="W24" s="19"/>
+      <c r="X24" s="19"/>
+      <c r="Y24" s="19"/>
+      <c r="Z24" s="19"/>
+      <c r="AA24" s="19"/>
+      <c r="AB24" s="19"/>
+      <c r="AC24" s="19"/>
+      <c r="AD24" s="19"/>
+      <c r="AE24" s="19"/>
+      <c r="AF24" s="19"/>
+      <c r="AG24" s="19"/>
+      <c r="AH24" s="19"/>
+      <c r="AI24" s="19"/>
+      <c r="AJ24" s="19"/>
+      <c r="AK24" s="19"/>
+      <c r="AL24" s="19"/>
+      <c r="AM24" s="19"/>
+      <c r="AN24" s="19"/>
+      <c r="AO24" s="19"/>
+      <c r="AP24" s="19"/>
+      <c r="AQ24" s="19"/>
+      <c r="AR24" s="19"/>
+      <c r="AS24" s="19"/>
+      <c r="AT24" s="19"/>
+      <c r="AU24" s="19"/>
+      <c r="AV24" s="19"/>
+      <c r="AW24" s="19"/>
+      <c r="AX24" s="20"/>
+      <c r="AY24" s="19"/>
+      <c r="AZ24" s="19"/>
+      <c r="BA24" s="19"/>
+      <c r="BB24" s="19"/>
     </row>
-    <row r="27" spans="1:54">
-      <c r="I27" s="29" t="s">
-        <v>115</v>
-      </c>
+    <row r="25" spans="1:54" s="2" customFormat="1" ht="15" customHeight="1" outlineLevel="1">
+      <c r="A25" s="23"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="J25" s="22"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="19"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="19"/>
+      <c r="X25" s="19"/>
+      <c r="Y25" s="19"/>
+      <c r="Z25" s="19"/>
+      <c r="AA25" s="19"/>
+      <c r="AB25" s="19"/>
+      <c r="AC25" s="19"/>
+      <c r="AD25" s="19"/>
+      <c r="AE25" s="19"/>
+      <c r="AF25" s="19"/>
+      <c r="AG25" s="19"/>
+      <c r="AH25" s="19"/>
+      <c r="AI25" s="19"/>
+      <c r="AJ25" s="19"/>
+      <c r="AK25" s="19"/>
+      <c r="AL25" s="19"/>
+      <c r="AM25" s="19"/>
+      <c r="AN25" s="19"/>
+      <c r="AO25" s="19"/>
+      <c r="AP25" s="19"/>
+      <c r="AQ25" s="19"/>
+      <c r="AR25" s="19"/>
+      <c r="AS25" s="19"/>
+      <c r="AT25" s="19"/>
+      <c r="AU25" s="19"/>
+      <c r="AV25" s="19"/>
+      <c r="AW25" s="19"/>
+      <c r="AX25" s="19"/>
+      <c r="AY25" s="19"/>
+      <c r="AZ25" s="19"/>
+      <c r="BA25" s="20"/>
+      <c r="BB25" s="19"/>
     </row>
     <row r="28" spans="1:54">
       <c r="I28" s="29" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:54">
       <c r="I29" s="29" t="s">
-        <v>117</v>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54">
+      <c r="I30" s="29" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54">
+      <c r="I31" s="29" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54">
+      <c r="I32" s="29" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
+    <mergeCell ref="I7:I9"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="I3:I5"/>
